--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.17026031055869</v>
+        <v>7.015167300465787</v>
       </c>
       <c r="D2" t="n">
-        <v>43.23190285378377</v>
+        <v>7.025184213739863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.911931285745375</v>
+        <v>0.1481888339336233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8759649740653686</v>
+        <v>0.1423443082856224</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.99412288204944</v>
+        <v>7.311544968333034</v>
       </c>
       <c r="D3" t="n">
-        <v>44.98383280191451</v>
+        <v>7.309872830311108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.911931285745375</v>
+        <v>0.1481888339336233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8759649740653686</v>
+        <v>0.1423443082856224</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
